--- a/output/sliding_window_results_window_3.xlsx
+++ b/output/sliding_window_results_window_3.xlsx
@@ -460,16 +460,16 @@
         <v>19</v>
       </c>
       <c r="B2" t="n">
-        <v>29.81</v>
+        <v>34.4</v>
       </c>
       <c r="C2" t="n">
-        <v>28.44027212647159</v>
+        <v>35.89362988192669</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.369727873528408</v>
+        <v>1.493629881926687</v>
       </c>
       <c r="E2" t="n">
-        <v>1.876154447520654</v>
+        <v>2.230930224184328</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>30.21</v>
+        <v>36.3</v>
       </c>
       <c r="C3" t="n">
-        <v>27.75937282280829</v>
+        <v>35.90045113407588</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.450627177191713</v>
+        <v>-0.3995488659241175</v>
       </c>
       <c r="E3" t="n">
-        <v>6.005573561590622</v>
+        <v>0.1596392962612485</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>30.48</v>
+        <v>38.5</v>
       </c>
       <c r="C4" t="n">
-        <v>28.86572137232448</v>
+        <v>39.82164025225872</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.614278627675521</v>
+        <v>1.321640252258717</v>
       </c>
       <c r="E4" t="n">
-        <v>2.605895487769963</v>
+        <v>1.746732956390486</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>30.95</v>
+        <v>40.1</v>
       </c>
       <c r="C5" t="n">
-        <v>29.76412542161936</v>
+        <v>43.60302207935992</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.185874578380638</v>
+        <v>3.503022079359916</v>
       </c>
       <c r="E5" t="n">
-        <v>1.406298515649455</v>
+        <v>12.27116368848307</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>31.38</v>
+        <v>41.5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.62783222439925</v>
+        <v>45.34288734468738</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7521677756007499</v>
+        <v>3.842887344687377</v>
       </c>
       <c r="E6" t="n">
-        <v>0.56575636265218</v>
+        <v>14.7677831439584</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>32.28</v>
+        <v>43.7</v>
       </c>
       <c r="C7" t="n">
-        <v>31.36584115144089</v>
+        <v>48.79430038903796</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9141588485591114</v>
+        <v>5.094300389037954</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8356864003989205</v>
+        <v>25.95189645375225</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>33.1</v>
+        <v>48.1</v>
       </c>
       <c r="C8" t="n">
-        <v>31.35199368098927</v>
+        <v>53.59051685073172</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.748006319010734</v>
+        <v>5.490516850731716</v>
       </c>
       <c r="E8" t="n">
-        <v>3.055526091301457</v>
+        <v>30.14577528816892</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>34.4</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>33.07928562366317</v>
+        <v>58.44230144910601</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.320714376336824</v>
+        <v>5.442301449106012</v>
       </c>
       <c r="E9" t="n">
-        <v>1.744286463862765</v>
+        <v>29.61864506294139</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>36.3</v>
+        <v>56.1</v>
       </c>
       <c r="C10" t="n">
-        <v>34.68873099962499</v>
+        <v>62.26014397251186</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.611269000375003</v>
+        <v>6.160143972511854</v>
       </c>
       <c r="E10" t="n">
-        <v>2.596187791569462</v>
+        <v>37.94737376207412</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>38.5</v>
+        <v>60</v>
       </c>
       <c r="C11" t="n">
-        <v>36.89198596683686</v>
+        <v>63.27113972267607</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.608014033163137</v>
+        <v>3.271139722676068</v>
       </c>
       <c r="E11" t="n">
-        <v>2.585709130849578</v>
+        <v>10.70035508526926</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="n">
-        <v>40.1</v>
+        <v>63.9</v>
       </c>
       <c r="C12" t="n">
-        <v>38.61442999096689</v>
+        <v>70.85872705862778</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.485570009033111</v>
+        <v>6.95872705862778</v>
       </c>
       <c r="E12" t="n">
-        <v>2.206918251738638</v>
+        <v>48.42388227647843</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>8</v>
       </c>
       <c r="B13" t="n">
-        <v>41.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>40.0325832391359</v>
+        <v>76.02160199556931</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.467416760864104</v>
+        <v>5.421601995569318</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1533119500649</v>
+        <v>29.39376819836122</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>43.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>43.30440840671626</v>
+        <v>82.86059403232137</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.395591593283747</v>
+        <v>1.960594032321367</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1564927086767735</v>
+        <v>3.843928959574159</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>6</v>
       </c>
       <c r="B15" t="n">
-        <v>48.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>45.01264194977922</v>
+        <v>84.88686389497401</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.087358050220786</v>
+        <v>-4.213136105025981</v>
       </c>
       <c r="E15" t="n">
-        <v>9.531779730263093</v>
+        <v>17.7505158394735</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>5</v>
       </c>
       <c r="B16" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C16" t="n">
-        <v>51.18789866201296</v>
+        <v>87.54140123957971</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.812101337987045</v>
+        <v>-7.458598760420287</v>
       </c>
       <c r="E16" t="n">
-        <v>3.283711259134438</v>
+        <v>55.63069546894305</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>56.1</v>
+        <v>98.8</v>
       </c>
       <c r="C17" t="n">
-        <v>54.33143903420413</v>
+        <v>99.45496398401421</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.768560965795871</v>
+        <v>0.6549639840142163</v>
       </c>
       <c r="E17" t="n">
-        <v>3.127807889736823</v>
+        <v>0.4289778203557746</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>60</v>
+        <v>103.3</v>
       </c>
       <c r="C18" t="n">
-        <v>57.45964451785933</v>
+        <v>101.4204415690728</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.540355482140669</v>
+        <v>-1.879558430927247</v>
       </c>
       <c r="E18" t="n">
-        <v>6.453405975642149</v>
+        <v>3.532739895269695</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>63.9</v>
+        <v>107</v>
       </c>
       <c r="C19" t="n">
-        <v>59.85010396546746</v>
+        <v>110.7129961570686</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.049896034532537</v>
+        <v>3.712996157068631</v>
       </c>
       <c r="E19" t="n">
-        <v>16.40165789052237</v>
+        <v>13.78634046240642</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>70.59999999999999</v>
+        <v>108.7</v>
       </c>
       <c r="C20" t="n">
-        <v>68.35164183083087</v>
+        <v>120.34297878296</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.248358169169123</v>
+        <v>11.64297878296003</v>
       </c>
       <c r="E20" t="n">
-        <v>5.055114456869529</v>
+        <v>135.5589549404574</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>80.90000000000001</v>
+        <v>112.7</v>
       </c>
       <c r="C21" t="n">
-        <v>77.77131188549247</v>
+        <v>122.7020448286416</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.12868811450754</v>
+        <v>10.0020448286416</v>
       </c>
       <c r="E21" t="n">
-        <v>9.788689317860744</v>
+        <v>100.0409007541562</v>
       </c>
     </row>
     <row r="22">
@@ -803,11 +803,11 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-36.55873512735637</v>
+        <v>62.02264661920161</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>81.43596368367452</v>
+        <v>573.9309995769593</v>
       </c>
     </row>
     <row r="23">
@@ -820,7 +820,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>4.071798184183725</v>
+        <v>28.69654997884796</v>
       </c>
     </row>
   </sheetData>
